--- a/NFLX.xlsx
+++ b/NFLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730E8068-BDAB-49DA-A179-B512556FBCD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAAE8D8-FB58-4276-8B15-D7EF3520BD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{D63826A5-B078-46BA-BBB8-108F6999A7DC}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{D63826A5-B078-46BA-BBB8-108F6999A7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -356,9 +356,6 @@
     <t>https://about.netflix.com/en/news/netflix-to-acquire-warner-bros</t>
   </si>
   <si>
-    <t>05-12-2025 Acqusition of Warner Bros Discovery for 82.7 Billion USD EV (72 Billion USD Equity Value)</t>
-  </si>
-  <si>
     <t>Deal with Open AI: 1 billion USD investment in Open AI, Disney Ips for Sora and GPT</t>
   </si>
   <si>
@@ -381,6 +378,9 @@
   </si>
   <si>
     <t>FY25</t>
+  </si>
+  <si>
+    <t>05-12-2025 Acqusition of Warner Bros Discovery for 82.7 Billion USD EV (72 Billion USD Equity Value) -&gt; lost biding war to PARA</t>
   </si>
 </sst>
 </file>
@@ -665,13 +665,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1052,7 +1052,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="12">
-        <v>86.07</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1068,7 +1068,7 @@
       <c r="I4" s="11">
         <v>4222.1621500000001</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="31" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I5" s="11">
         <f>I4*I3</f>
-        <v>363401.49625049997</v>
+        <v>411660.80962499999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1092,7 +1092,7 @@
         <f>9033.681+28.678</f>
         <v>9062.3590000000004</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="31" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
         <f>998.865+13463.971</f>
         <v>14462.835999999999</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="J7" s="31" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I8" s="11">
         <f>I5-I6+I7</f>
-        <v>368801.97325049998</v>
+        <v>417061.28662500001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1170,8 +1170,8 @@
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" s="30" t="s">
-        <v>77</v>
+      <c r="B18" s="33" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
@@ -1180,8 +1180,8 @@
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B20" s="31" t="s">
-        <v>78</v>
+      <c r="B20" s="30" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1245,26 +1245,26 @@
       <c r="N2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="P2" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="Q2" s="32" t="s">
+      <c r="R2" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="32" t="s">
+      <c r="S2" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="32" t="s">
+      <c r="T2" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="T2" s="32" t="s">
+      <c r="U2" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="U2" s="32" t="s">
+      <c r="V2" s="31" t="s">
         <v>84</v>
-      </c>
-      <c r="V2" s="32" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:62" x14ac:dyDescent="0.2">
@@ -3956,13 +3956,13 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
       <c r="S30" s="11"/>
-      <c r="T30" s="33" t="s">
+      <c r="T30" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="U30" s="33" t="s">
+      <c r="U30" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="V30" s="33" t="s">
+      <c r="V30" s="32" t="s">
         <v>74</v>
       </c>
       <c r="W30" s="11"/>

--- a/NFLX.xlsx
+++ b/NFLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E6C3EB-8D0A-45E5-B6B8-AF5245A2AC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349CE9AF-C615-4133-89D3-19F55A2D2C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D63826A5-B078-46BA-BBB8-108F6999A7DC}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D63826A5-B078-46BA-BBB8-108F6999A7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="90">
   <si>
     <t>Netflix</t>
   </si>
@@ -404,13 +404,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -642,57 +648,61 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1073,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="I3" s="12">
-        <v>97.5</v>
+        <v>69.17</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1087,10 +1097,10 @@
         <v>4</v>
       </c>
       <c r="I4" s="11">
-        <v>4222.7870000000003</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>86</v>
+        <v>4163.939676</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1102,7 +1112,7 @@
       </c>
       <c r="I5" s="11">
         <f>I4*I3</f>
-        <v>411721.73250000004</v>
+        <v>288019.70738892001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -1110,11 +1120,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="11">
-        <f>12259.772+28.678</f>
-        <v>12288.45</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>86</v>
+        <f>9099.232+28.678</f>
+        <v>9127.91</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1128,11 +1138,11 @@
         <v>7</v>
       </c>
       <c r="I7" s="29">
-        <f>13361.331+999.185</f>
-        <v>14360.516</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>86</v>
+        <f>11825.548+2483.758</f>
+        <v>14309.306</v>
+      </c>
+      <c r="J7" s="35" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1151,7 +1161,7 @@
       </c>
       <c r="I8" s="11">
         <f>I5-I6+I7</f>
-        <v>413793.79850000003</v>
+        <v>293201.10338892002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1344,7 +1354,9 @@
       <c r="O3" s="11">
         <v>5245.2979999999998</v>
       </c>
-      <c r="P3" s="11"/>
+      <c r="P3" s="11">
+        <v>5431.6670000000004</v>
+      </c>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
       <c r="S3" s="11"/>
@@ -1445,7 +1457,9 @@
       <c r="O4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="13"/>
+      <c r="P4" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q4" s="13"/>
       <c r="R4" s="13"/>
       <c r="S4" s="11"/>
@@ -1547,7 +1561,9 @@
       <c r="O5" s="11">
         <v>3998.4189999999999</v>
       </c>
-      <c r="P5" s="11"/>
+      <c r="P5" s="11">
+        <v>4033.5149999999999</v>
+      </c>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
@@ -1648,7 +1664,9 @@
       <c r="O6" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P6" s="13"/>
+      <c r="P6" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
       <c r="S6" s="11"/>
@@ -1750,7 +1768,9 @@
       <c r="O7" s="11">
         <v>1497.058</v>
       </c>
-      <c r="P7" s="11"/>
+      <c r="P7" s="11">
+        <v>1584.29</v>
+      </c>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
@@ -1851,7 +1871,9 @@
       <c r="O8" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P8" s="13"/>
+      <c r="P8" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q8" s="13"/>
       <c r="R8" s="13"/>
       <c r="S8" s="11"/>
@@ -1953,7 +1975,9 @@
       <c r="O9" s="11">
         <v>1508.982</v>
       </c>
-      <c r="P9" s="11"/>
+      <c r="P9" s="11">
+        <v>1510.4659999999999</v>
+      </c>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
       <c r="S9" s="11"/>
@@ -2054,7 +2078,9 @@
       <c r="O10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q10" s="13"/>
       <c r="R10" s="13"/>
       <c r="S10" s="11"/>
@@ -2161,7 +2187,9 @@
       <c r="O11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
       <c r="S11" s="11"/>
@@ -2270,7 +2298,9 @@
       <c r="O12" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
       <c r="S12" s="11"/>
@@ -2372,7 +2402,9 @@
       <c r="O13" s="15">
         <v>12249.757</v>
       </c>
-      <c r="P13" s="15"/>
+      <c r="P13" s="15">
+        <v>12559.938</v>
+      </c>
       <c r="Q13" s="15"/>
       <c r="R13" s="15"/>
       <c r="S13" s="11"/>
@@ -2474,7 +2506,9 @@
       <c r="O14" s="11">
         <v>5888.2380000000003</v>
       </c>
-      <c r="P14" s="11"/>
+      <c r="P14" s="11">
+        <v>6036.9650000000001</v>
+      </c>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
       <c r="S14" s="11"/>
@@ -2545,7 +2579,7 @@
         <v>3513.8310000000001</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" ref="E15:O15" si="1">E13-E14</f>
+        <f t="shared" ref="E15:P15" si="1">E13-E14</f>
         <v>3610.8899999999994</v>
       </c>
       <c r="F15" s="11">
@@ -2588,7 +2622,10 @@
         <f t="shared" si="1"/>
         <v>6361.5189999999993</v>
       </c>
-      <c r="P15" s="11"/>
+      <c r="P15" s="11">
+        <f t="shared" si="1"/>
+        <v>6522.973</v>
+      </c>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
@@ -2693,7 +2730,9 @@
       <c r="O16" s="11">
         <v>842.21699999999998</v>
       </c>
-      <c r="P16" s="11"/>
+      <c r="P16" s="11">
+        <v>823.83799999999997</v>
+      </c>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
@@ -2795,7 +2834,9 @@
       <c r="O17" s="11">
         <v>959.69500000000005</v>
       </c>
-      <c r="P17" s="11"/>
+      <c r="P17" s="11">
+        <v>1007.675</v>
+      </c>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
@@ -2897,7 +2938,9 @@
       <c r="O18" s="11">
         <v>602.60900000000004</v>
       </c>
-      <c r="P18" s="11"/>
+      <c r="P18" s="11">
+        <v>498.85</v>
+      </c>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
       <c r="S18" s="11"/>
@@ -2984,7 +3027,7 @@
         <v>2602.8369999999995</v>
       </c>
       <c r="I19" s="11">
-        <f t="shared" ref="I19:O19" si="4">I15-SUM(I16:I18)</f>
+        <f t="shared" ref="I19:P19" si="4">I15-SUM(I16:I18)</f>
         <v>2909.4769999999994</v>
       </c>
       <c r="J19" s="11">
@@ -3011,7 +3054,10 @@
         <f t="shared" si="4"/>
         <v>3956.9979999999991</v>
       </c>
-      <c r="P19" s="11"/>
+      <c r="P19" s="11">
+        <f t="shared" si="4"/>
+        <v>4192.6100000000006</v>
+      </c>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
       <c r="S19" s="11"/>
@@ -3128,7 +3174,9 @@
       <c r="O20" s="11">
         <v>262.077</v>
       </c>
-      <c r="P20" s="11"/>
+      <c r="P20" s="11">
+        <v>175.685</v>
+      </c>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
       <c r="S20" s="11"/>
@@ -3230,7 +3278,9 @@
       <c r="O21" s="11">
         <v>2852.1660000000002</v>
       </c>
-      <c r="P21" s="11"/>
+      <c r="P21" s="11">
+        <v>51.661000000000001</v>
+      </c>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
       <c r="S21" s="11"/>
@@ -3317,7 +3367,7 @@
         <v>2513.8559999999998</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" ref="I22:O22" si="7">I19-I20+I21</f>
+        <f t="shared" ref="I22:P22" si="7">I19-I20+I21</f>
         <v>2702.9539999999993</v>
       </c>
       <c r="J22" s="11">
@@ -3344,7 +3394,10 @@
         <f t="shared" si="7"/>
         <v>6547.0869999999995</v>
       </c>
-      <c r="P22" s="11"/>
+      <c r="P22" s="11">
+        <f t="shared" si="7"/>
+        <v>4068.5860000000007</v>
+      </c>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
@@ -3461,7 +3514,9 @@
       <c r="O23" s="11">
         <v>1264.2950000000001</v>
       </c>
-      <c r="P23" s="11"/>
+      <c r="P23" s="11">
+        <v>667.17200000000003</v>
+      </c>
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
       <c r="S23" s="11"/>
@@ -3568,14 +3623,17 @@
         <v>2546.9160000000006</v>
       </c>
       <c r="N24" s="11">
-        <f t="shared" ref="N24:O24" si="11">N22-N23</f>
+        <f t="shared" ref="N24:P24" si="11">N22-N23</f>
         <v>2418.3219999999988</v>
       </c>
       <c r="O24" s="11">
         <f t="shared" si="11"/>
         <v>5282.7919999999995</v>
       </c>
-      <c r="P24" s="11"/>
+      <c r="P24" s="11">
+        <f t="shared" si="11"/>
+        <v>3401.4140000000007</v>
+      </c>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="11"/>
@@ -3743,7 +3801,7 @@
         <v>4.9929801309104427</v>
       </c>
       <c r="I26" s="14">
-        <f t="shared" ref="I26:O26" si="14">I24/I27</f>
+        <f t="shared" ref="I26:P26" si="14">I24/I27</f>
         <v>5.519135342647445</v>
       </c>
       <c r="J26" s="14">
@@ -3770,7 +3828,10 @@
         <f t="shared" si="14"/>
         <v>1.2510202385296723</v>
       </c>
-      <c r="P26" s="14"/>
+      <c r="P26" s="14">
+        <f t="shared" si="14"/>
+        <v>0.81192838044896742</v>
+      </c>
       <c r="Q26" s="14"/>
       <c r="R26" s="14"/>
       <c r="S26" s="11"/>
@@ -3883,7 +3944,9 @@
       <c r="O27" s="11">
         <v>4222.7870000000003</v>
       </c>
-      <c r="P27" s="11"/>
+      <c r="P27" s="36">
+        <v>4189.3029999999999</v>
+      </c>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
       <c r="S27" s="11"/>
@@ -4024,7 +4087,7 @@
         <v>0.16757769135396372</v>
       </c>
       <c r="I29" s="8">
-        <f t="shared" ref="I29:O29" si="17">I13/E13-1</f>
+        <f t="shared" ref="I29:P29" si="17">I13/E13-1</f>
         <v>0.15020895216250496</v>
       </c>
       <c r="J29" s="8">
@@ -4051,7 +4114,10 @@
         <f t="shared" si="17"/>
         <v>0.16188532675708989</v>
       </c>
-      <c r="P29" s="8"/>
+      <c r="P29" s="8">
+        <f t="shared" si="17"/>
+        <v>0.13365374252899542</v>
+      </c>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
       <c r="S29" s="11"/>
@@ -4151,7 +4217,9 @@
       <c r="O30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="P30" s="13"/>
+      <c r="P30" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
       <c r="S30" s="11"/>
@@ -4262,10 +4330,13 @@
         <v>0.4587289407142221</v>
       </c>
       <c r="O31" s="5">
-        <f t="shared" ref="O31" si="25">O15/O13</f>
+        <f t="shared" ref="O31:P31" si="25">O15/O13</f>
         <v>0.51931797504228039</v>
       </c>
-      <c r="P31" s="5"/>
+      <c r="P31" s="5">
+        <f t="shared" si="25"/>
+        <v>0.51934754773471015</v>
+      </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="11"/>
@@ -4391,10 +4462,13 @@
         <v>0.24533824685203492</v>
       </c>
       <c r="O32" s="5">
-        <f t="shared" ref="O32" si="31">O19/O13</f>
+        <f t="shared" ref="O32:P32" si="31">O19/O13</f>
         <v>0.32302665269196762</v>
       </c>
-      <c r="P32" s="5"/>
+      <c r="P32" s="5">
+        <f t="shared" si="31"/>
+        <v>0.33380817644163535</v>
+      </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="11"/>
@@ -4520,10 +4594,13 @@
         <v>0.12618417353738456</v>
       </c>
       <c r="O33" s="5">
-        <f t="shared" ref="O33" si="37">O23/O22</f>
+        <f t="shared" ref="O33:P33" si="37">O23/O22</f>
         <v>0.19310801887923593</v>
       </c>
-      <c r="P33" s="5"/>
+      <c r="P33" s="5">
+        <f t="shared" si="37"/>
+        <v>0.16398129472991352</v>
+      </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="11"/>
